--- a/컬리주문_등록양식.xlsx
+++ b/컬리주문_등록양식.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gyu89\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mk-am14-012/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16813BC-B2B8-4841-96CD-E5A7EF360F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{344D8DF1-C045-9B47-93BE-42EDE3C104C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2040" yWindow="760" windowWidth="28000" windowHeight="18660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="사용방법 및 예시(실제 주문은 우측 탭에 작성 요망)" sheetId="1" r:id="rId1"/>
@@ -209,10 +209,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>샛별배송</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -868,26 +864,6 @@
   </si>
   <si>
     <t>당일배송</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>샛별배송 
-2. 당일배송 
-3. 하루배송
-4. 자동</t>
-    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -1238,6 +1214,30 @@
       </rPr>
       <t>)</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>새벽배송 
+2. 당일배송 
+3. 하루배송
+4. 자동</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>새벽배송</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1785,7 +1785,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N9"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="14" width="20" customWidth="1"/>
   </cols>
@@ -1868,35 +1868,35 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="79.5">
+    <row r="4" spans="1:14" ht="86">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="19" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J4" s="5"/>
       <c r="K4" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1910,7 +1910,7 @@
         <v>6</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>7</v>
@@ -1922,7 +1922,7 @@
         <v>9</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>10</v>
@@ -1954,7 +1954,7 @@
         <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
@@ -1966,7 +1966,7 @@
         <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I6" t="s">
         <v>21</v>
@@ -1975,7 +1975,7 @@
         <v>22</v>
       </c>
       <c r="K6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L6" t="s">
         <v>23</v>
@@ -1998,7 +1998,7 @@
         <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
         <v>19</v>
@@ -2010,7 +2010,7 @@
         <v>20</v>
       </c>
       <c r="H7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I7" t="s">
         <v>21</v>
@@ -2019,7 +2019,7 @@
         <v>26</v>
       </c>
       <c r="K7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L7" t="s">
         <v>23</v>
@@ -2042,7 +2042,7 @@
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
         <v>19</v>
@@ -2054,7 +2054,7 @@
         <v>20</v>
       </c>
       <c r="H8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I8" t="s">
         <v>21</v>
@@ -2063,7 +2063,7 @@
         <v>29</v>
       </c>
       <c r="K8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L8" t="s">
         <v>23</v>
@@ -2080,13 +2080,13 @@
         <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
         <v>19</v>
@@ -2098,7 +2098,7 @@
         <v>20</v>
       </c>
       <c r="H9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I9" t="s">
         <v>21</v>
@@ -2107,7 +2107,7 @@
         <v>29</v>
       </c>
       <c r="K9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M9" t="s">
         <v>24</v>
@@ -2125,7 +2125,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N1000"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="2" width="20" style="14" customWidth="1"/>
     <col min="3" max="3" width="20" style="12" customWidth="1"/>
@@ -2140,40 +2140,40 @@
         <v>33</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C1" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>41</v>
-      </c>
       <c r="G1" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H1" s="20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I1" s="17" t="s">
         <v>30</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K1" s="21" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L1" s="17" t="s">
         <v>31</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N1" s="17" t="s">
         <v>32</v>
@@ -6181,7 +6181,7 @@
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{0A1DA9C8-49D8-F944-A62B-824B60F2E88B}">
-      <formula1>"샛별배송,당일배송,하루배송,자동"</formula1>
+      <formula1>"새벽배송,당일배송,하루배송,자동"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K1048576" xr:uid="{C5340D97-77F7-264E-8A19-178D3B4B4D2D}">
       <formula1>"문 앞,택배 수령실,공동현관(대문) 앞,기타  "</formula1>
